--- a/data/trans_bre/P1423-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,11</t>
+          <t>1,14; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,5</t>
+          <t>-0,57; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,21</t>
+          <t>0,26; 4,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 8,82</t>
+          <t>-0,48; 8,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 778,28</t>
+          <t>-66,11; 831,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-15,44; 1169,67</t>
+          <t>-11,64; 1166,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 1132,21</t>
+          <t>-30,37; 1055,23</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,39</t>
+          <t>-0,09; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,62</t>
+          <t>-0,91; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,98</t>
+          <t>-0,13; 2,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,82</t>
+          <t>0,9; 7,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 249,35</t>
+          <t>-12,62; 260,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 172,93</t>
+          <t>-23,76; 181,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 474,77</t>
+          <t>-15,43; 480,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 473,42</t>
+          <t>14,64; 504,64</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,01</t>
+          <t>0,52; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,71</t>
+          <t>3,03; 8,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,46</t>
+          <t>2,16; 6,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,09</t>
+          <t>-1,76; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,09; 239,29</t>
+          <t>9,96; 257,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,98; 330,85</t>
+          <t>50,64; 311,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,36; 397,77</t>
+          <t>55,26; 438,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,03; 91,55</t>
+          <t>-22,38; 97,62</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 11,21</t>
+          <t>5,03; 11,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,95; 11,32</t>
+          <t>4,85; 11,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,73; 10,86</t>
+          <t>4,93; 11,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,39</t>
+          <t>3,59; 11,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>119,44; 607,12</t>
+          <t>120,09; 582,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,0; 346,35</t>
+          <t>80,04; 340,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,08; 340,89</t>
+          <t>91,01; 374,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,87; 400,23</t>
+          <t>43,1; 431,82</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 11,33</t>
+          <t>3,2; 11,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 15,63</t>
+          <t>6,64; 16,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 15,63</t>
+          <t>7,12; 15,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 11,29</t>
+          <t>4,38; 11,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,84; 283,61</t>
+          <t>43,28; 294,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,65; 292,89</t>
+          <t>66,88; 287,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,45; 322,94</t>
+          <t>81,47; 328,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,57; 142,21</t>
+          <t>37,24; 139,85</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,44; 10,74</t>
+          <t>2,1; 10,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,48; 19,32</t>
+          <t>8,6; 18,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,26; 19,07</t>
+          <t>10,0; 19,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 11,96</t>
+          <t>-0,91; 12,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33,83; 304,89</t>
+          <t>24,39; 298,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114,61; 580,97</t>
+          <t>102,28; 561,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>235,97; 1243,63</t>
+          <t>221,42; 1250,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 279,64</t>
+          <t>-12,83; 289,42</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,4</t>
+          <t>-2,36; 7,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 17,27</t>
+          <t>6,61; 17,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,48</t>
+          <t>4,12; 14,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 10,59</t>
+          <t>3,6; 11,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,63; 186,82</t>
+          <t>-27,79; 181,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,43; 408,29</t>
+          <t>60,93; 397,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,36; 352,96</t>
+          <t>44,45; 341,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,8; 148,76</t>
+          <t>33,22; 156,82</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,61</t>
+          <t>3,4; 5,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,83; 8,42</t>
+          <t>6,01; 8,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,11</t>
+          <t>5,78; 8,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,9</t>
+          <t>3,37; 7,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,3; 209,38</t>
+          <t>95,87; 207,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>121,93; 235,6</t>
+          <t>129,22; 239,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>156,24; 293,11</t>
+          <t>153,38; 285,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,36; 143,15</t>
+          <t>56,85; 149,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1423-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1423-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>180,33%</t>
+          <t>119,81%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,34</t>
+          <t>1,01; 4,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,39</t>
+          <t>-0,56; 2,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,35</t>
+          <t>0,21; 4,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 8,94</t>
+          <t>-1,07; 6,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 831,83</t>
+          <t>-70,66; 670,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 1166,6</t>
+          <t>-25,58; 1065,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 1055,23</t>
+          <t>-41,48; 592,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,97</t>
+          <t>4,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>155,97%</t>
+          <t>133,84%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 3,41</t>
+          <t>-0,1; 3,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,53</t>
+          <t>-0,71; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,9</t>
+          <t>-0,11; 2,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,23</t>
+          <t>1,15; 7,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 260,24</t>
+          <t>-7,59; 253,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 181,91</t>
+          <t>-22,54; 156,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 480,54</t>
+          <t>-16,85; 448,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,64; 504,64</t>
+          <t>14,5; 430,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>46,22%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,15</t>
+          <t>0,45; 5,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,69</t>
+          <t>3,18; 8,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,82</t>
+          <t>2,3; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,16</t>
+          <t>-0,29; 4,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,96; 257,33</t>
+          <t>3,44; 238,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>50,64; 311,64</t>
+          <t>59,74; 314,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,26; 438,91</t>
+          <t>60,74; 401,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,38; 97,62</t>
+          <t>-4,44; 119,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>126,45%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 11,46</t>
+          <t>4,84; 11,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,38</t>
+          <t>4,92; 11,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,02</t>
+          <t>4,73; 10,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 11,73</t>
+          <t>2,42; 8,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>120,09; 582,42</t>
+          <t>105,93; 601,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,04; 340,38</t>
+          <t>81,23; 326,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,01; 374,64</t>
+          <t>83,42; 361,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,1; 431,82</t>
+          <t>26,56; 137,78</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,99</t>
+          <t>8,44</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,37</t>
+          <t>3,1; 11,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 16,02</t>
+          <t>6,85; 15,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,12; 15,62</t>
+          <t>7,02; 15,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 11,1</t>
+          <t>4,92; 11,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>43,28; 294,38</t>
+          <t>42,75; 265,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,88; 287,81</t>
+          <t>71,06; 291,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,47; 328,1</t>
+          <t>83,26; 324,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,24; 139,85</t>
+          <t>44,86; 151,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,61</t>
+          <t>11,28</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>118,22%</t>
+          <t>250,28%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,61</t>
+          <t>2,46; 10,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,6; 18,8</t>
+          <t>9,21; 19,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,0; 19,02</t>
+          <t>10,2; 19,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 12,14</t>
+          <t>8,15; 14,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,39; 298,92</t>
+          <t>30,8; 305,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>102,28; 561,47</t>
+          <t>103,35; 532,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>221,42; 1250,52</t>
+          <t>224,8; 1251,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 289,42</t>
+          <t>129,38; 439,83</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,19</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,77</t>
+          <t>-2,16; 7,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,61; 17,33</t>
+          <t>6,09; 17,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,06</t>
+          <t>4,35; 14,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,6; 11,12</t>
+          <t>3,35; 10,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 181,57</t>
+          <t>-23,77; 166,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,93; 397,08</t>
+          <t>51,6; 403,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,45; 341,3</t>
+          <t>52,42; 338,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,22; 156,82</t>
+          <t>28,4; 159,14</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,42</t>
+          <t>6,13</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>100,74%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,59</t>
+          <t>3,38; 5,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,55</t>
+          <t>5,94; 8,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,78; 8,17</t>
+          <t>5,69; 8,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,03</t>
+          <t>4,9; 7,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>95,87; 207,45</t>
+          <t>94,2; 210,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>129,22; 239,44</t>
+          <t>125,35; 236,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>153,38; 285,53</t>
+          <t>154,23; 286,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,85; 149,75</t>
+          <t>71,33; 133,31</t>
         </is>
       </c>
     </row>
